--- a/spreadsheets/domains/cramps-eng_CRAMPS-ENG_Workbook.xlsx
+++ b/spreadsheets/domains/cramps-eng_CRAMPS-ENG_Workbook.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R2603759abf914010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R5d073b73f8ac485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R2254a672f60c4392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rc42d67cdc9ee4fdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R9c784bcbbcbc4237"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="Rba507a076bd14107"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Ra6a75d548d3e438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R74caaefddb224aea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Rd06f0b60bc0b4af3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R8cd5bf6ec0844e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R434a6401c8f4466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="Rf1854797fe714afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rea55338bc18a436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Rb6f9acdb659144bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Failure Modes" sheetId="5" r:id="R47e33b3728e9459a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R94280179b46242f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R7778a474037441f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rafe1c6812c20444c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="R3c1cabf238254b5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="Re3d6e11a3b7e47be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -250,7 +250,7 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Gotchas</x:v>
+        <x:v>Primary failure modes</x:v>
       </x:c>
       <x:c r="B7" t="str">
         <x:v>fleet exposure imbalance; maintenance censoring; supplier-lot dependence; sensor drift</x:v>
@@ -1089,7 +1089,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>Gotcha</x:v>
+        <x:v>Failure mode</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Status</x:v>
@@ -1255,7 +1255,7 @@
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
+        <x:v>raw signal rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
